--- a/excel_results/BOM_media_1788593034536.xlsx
+++ b/excel_results/BOM_media_1788593034536.xlsx
@@ -718,7 +718,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-06  13:27:07   |   Antigravity BOM Extractor</t>
+          <t>Generated: 2026-09-07  13:44:35   |   Antigravity BOM Extractor</t>
         </is>
       </c>
     </row>
